--- a/Result/profitability/6138.xlsx
+++ b/Result/profitability/6138.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75375</v>
+        <v>2.91125</v>
       </c>
       <c r="N2" t="n">
-        <v>34.275</v>
+        <v>34.64625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4775</v>
+        <v>2.675</v>
       </c>
       <c r="N3" t="n">
-        <v>32.24125</v>
+        <v>32.6975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2875</v>
+        <v>2.4575</v>
       </c>
       <c r="N4" t="n">
-        <v>30.66</v>
+        <v>31.27</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>2.0575</v>
       </c>
       <c r="N5" t="n">
-        <v>28.17</v>
+        <v>28.745</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.57</v>
+        <v>1.56875</v>
       </c>
       <c r="N6" t="n">
-        <v>26.5175</v>
+        <v>26.80625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12875</v>
+        <v>1.1525</v>
       </c>
       <c r="N7" t="n">
-        <v>24.98</v>
+        <v>25.01125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.75625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.91375</v>
+        <v>22.985</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2064</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E75" t="n">
+        <v>804</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>410</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>45</v>
+      </c>
+      <c r="J75" t="n">
+        <v>455</v>
+      </c>
+      <c r="K75" t="n">
+        <v>290</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.55625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2799999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.07608695652173902</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01484761656681433</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1338766006984866</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
